--- a/stats for com eng/excel files/Ch4-02.xlsx
+++ b/stats for com eng/excel files/Ch4-02.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5C42A7-DB3E-0644-A54F-49A75AF0C995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E688876-F75D-1948-958B-12CBCF22CBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="24080" windowHeight="13160" activeTab="1" xr2:uid="{4C1FC052-56B3-4703-985E-36351D15350F}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11000" activeTab="3" xr2:uid="{4C1FC052-56B3-4703-985E-36351D15350F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1 practice" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2 practice" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$3</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$A$4:$A$25</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Sheet1 practice'!$A$3</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Sheet1 practice'!$A$4:$A$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
   <si>
     <t>Alloy Adhesion</t>
   </si>
@@ -211,6 +215,42 @@
   <si>
     <t>TRYING TO FIND TRUE POPULATION VARIANCE, FINDING INTERVAL</t>
   </si>
+  <si>
+    <t>n&gt;=30 switch to z test</t>
+  </si>
+  <si>
+    <t>t (alpha/2) critical value</t>
+  </si>
+  <si>
+    <t>critical value</t>
+  </si>
+  <si>
+    <t>test stats</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>p value</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>exact coordinate</t>
+  </si>
+  <si>
+    <t>Formulas in confidence bound is made for pos value</t>
+  </si>
+  <si>
+    <t>so right tail</t>
+  </si>
+  <si>
+    <t>critical value, alpha from right</t>
+  </si>
+  <si>
+    <t>critical value, 1-alpha from right</t>
+  </si>
 </sst>
 </file>
 
@@ -219,7 +259,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +302,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -320,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -340,6 +387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -373,6 +421,46 @@
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.0</cx:f>
+              <cx:v>Load (megapascals)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.3</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{F2886E6D-E392-4ECF-A49B-C36E1E8B2424}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Load (megapascals)</cx:v>
             </cx:txData>
           </cx:tx>
@@ -437,7 +525,562 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1081,6 +1724,177 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D081ED08-2DBE-6A47-8A98-D344F5F7B9C6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2032000" y="428625"/>
+              <a:ext cx="2095500" cy="2197100"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>22478</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>78672</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>377179</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>62783</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E08FD2E-FCC4-6B49-85C2-CCA3C399A2A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5229478" y="459672"/>
+          <a:ext cx="7758801" cy="2651111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>573139</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>49282</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428810</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>79047</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E489EFAB-C59E-103D-2C3B-2319BA9830F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="573139" y="5647442"/>
+          <a:ext cx="7739831" cy="2732325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1168,6 +1982,116 @@
         <a:xfrm>
           <a:off x="4159250" y="1600201"/>
           <a:ext cx="2520563" cy="1644650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>28576</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>86690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED5218C5-9D73-8847-BE31-3BE67BFB4BA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3228976" y="438150"/>
+          <a:ext cx="4073524" cy="1007440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>492125</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>574288</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Chi-Square Table - Statistics By Jim">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C7F4A8-40A5-104F-ACFB-805D6BFFAA7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4505325" y="1641476"/>
+          <a:ext cx="2774563" cy="1733550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1705,6 +2629,250 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06FE082D-12E7-8444-9EC2-93FCDBA47E60}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6">
+        <f>AVERAGE(A4:A25)</f>
+        <v>13.713636363636358</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6">
+        <f>_xlfn.STDEV.S(A4:A25)</f>
+        <v>3.5535757249424997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>11.9</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="5">
+        <f>1-0.95</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>15.4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="3">
+        <f>D19/2</f>
+        <v>2.5000000000000022E-2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>11.9</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="5">
+        <f>COUNT(A4:A25)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="3">
+        <f>D21-1</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>11.4</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="6">
+        <f>_xlfn.T.INV(1-D20, D22)</f>
+        <v>2.07961384472768</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23">
+        <f>_xlfn.T.INV.2T(D19, D21-1)</f>
+        <v>2.07961384472768</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>15.4</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="6">
+        <f>D16-D23*D17/SQRT(D21)</f>
+        <v>12.138069152904313</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>11.4</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="6">
+        <f>D16+D23*D17/SQRT(D21)</f>
+        <v>15.289203574368402</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95CF4E87-E7D3-44EF-8D4F-CFD7AAE28FEB}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1802,4 +2970,121 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550D4848-3616-B947-80DA-4FD44AE11117}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="4" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1.5299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <f>B3-1</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="6">
+        <f>(B3-1)*B4/C14</f>
+        <v>2.8733777268556287E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="6">
+        <f>SQRT(D10)</f>
+        <v>0.16951040460265643</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <f>_xlfn.CHISQ.INV.RT(B6, B7)</f>
+        <v>30.143527205646155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14">
+        <f>_xlfn.CHISQ.INV.RT(1-B6, B7)</f>
+        <v>10.117013063859044</v>
+      </c>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:C10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>